--- a/order_forms/022_purchase_requisition_authorization_form--order_forms.xlsx
+++ b/order_forms/022_purchase_requisition_authorization_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'jim_smith'}</t>
+          <t>jim_smith</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Jim Smith'}</t>
+          <t>Jim Smith</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'pending_approval'}</t>
+          <t>pending_approval</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Pending Approval'}</t>
+          <t>Pending Approval</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
